--- a/output/2nf.xlsx
+++ b/output/2nf.xlsx
@@ -8,9 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="orders" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="customers" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="products" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="order_items" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="products" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="order_items" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C298"/>
+  <dimension ref="A1:F298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +446,21 @@
           <t>customer_id</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>customer_name</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>customer_age</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>customer_gender</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -460,6 +474,19 @@
       <c r="C2" t="n">
         <v>74</v>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -473,6 +500,19 @@
       <c r="C3" t="n">
         <v>54</v>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -486,6 +526,19 @@
       <c r="C4" t="n">
         <v>71</v>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>42</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -499,6 +552,19 @@
       <c r="C5" t="n">
         <v>56</v>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>53</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -512,6 +578,19 @@
       <c r="C6" t="n">
         <v>79</v>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Ayaan</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>32</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -525,6 +604,19 @@
       <c r="C7" t="n">
         <v>16</v>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Ananya</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>32</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -538,6 +630,19 @@
       <c r="C8" t="n">
         <v>29</v>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>53</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -551,6 +656,19 @@
       <c r="C9" t="n">
         <v>47</v>
       </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>44</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -564,6 +682,19 @@
       <c r="C10" t="n">
         <v>61</v>
       </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>29</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -577,6 +708,19 @@
       <c r="C11" t="n">
         <v>27</v>
       </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Kavya</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>41</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -590,6 +734,19 @@
       <c r="C12" t="n">
         <v>73</v>
       </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>29</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -603,6 +760,19 @@
       <c r="C13" t="n">
         <v>58</v>
       </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>29</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -616,6 +786,19 @@
       <c r="C14" t="n">
         <v>89</v>
       </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Aarav</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>37</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -629,6 +812,19 @@
       <c r="C15" t="n">
         <v>58</v>
       </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>29</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -642,6 +838,19 @@
       <c r="C16" t="n">
         <v>22</v>
       </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Ishita</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>18</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -655,6 +864,19 @@
       <c r="C17" t="n">
         <v>50</v>
       </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>18</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -668,6 +890,19 @@
       <c r="C18" t="n">
         <v>98</v>
       </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>28</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -681,6 +916,19 @@
       <c r="C19" t="n">
         <v>13</v>
       </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Vihaan</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>22</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -694,6 +942,19 @@
       <c r="C20" t="n">
         <v>83</v>
       </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ria</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>38</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -707,6 +968,19 @@
       <c r="C21" t="n">
         <v>67</v>
       </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>24</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -720,6 +994,19 @@
       <c r="C22" t="n">
         <v>76</v>
       </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Mia</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -733,6 +1020,19 @@
       <c r="C23" t="n">
         <v>12</v>
       </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>52</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -746,6 +1046,19 @@
       <c r="C24" t="n">
         <v>10</v>
       </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Simran</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>32</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -759,6 +1072,19 @@
       <c r="C25" t="n">
         <v>43</v>
       </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>35</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -772,6 +1098,19 @@
       <c r="C26" t="n">
         <v>92</v>
       </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>18</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -785,6 +1124,19 @@
       <c r="C27" t="n">
         <v>64</v>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Dhruv</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>28</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -798,6 +1150,19 @@
       <c r="C28" t="n">
         <v>89</v>
       </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Aarav</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>37</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -811,6 +1176,19 @@
       <c r="C29" t="n">
         <v>52</v>
       </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Aditi</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>36</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -824,6 +1202,19 @@
       <c r="C30" t="n">
         <v>52</v>
       </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Aditi</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>36</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -837,6 +1228,19 @@
       <c r="C31" t="n">
         <v>68</v>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>21</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -850,6 +1254,19 @@
       <c r="C32" t="n">
         <v>92</v>
       </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>18</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -863,6 +1280,19 @@
       <c r="C33" t="n">
         <v>47</v>
       </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>44</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -876,6 +1306,19 @@
       <c r="C34" t="n">
         <v>28</v>
       </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>39</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -889,6 +1332,19 @@
       <c r="C35" t="n">
         <v>62</v>
       </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Aryan</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>27</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -902,6 +1358,19 @@
       <c r="C36" t="n">
         <v>10</v>
       </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Simran</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>32</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -915,6 +1384,19 @@
       <c r="C37" t="n">
         <v>54</v>
       </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>33</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -928,6 +1410,19 @@
       <c r="C38" t="n">
         <v>10</v>
       </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Simran</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>32</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -941,6 +1436,19 @@
       <c r="C39" t="n">
         <v>13</v>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Vihaan</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>22</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -954,6 +1462,19 @@
       <c r="C40" t="n">
         <v>38</v>
       </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Meera</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>31</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -967,6 +1488,19 @@
       <c r="C41" t="n">
         <v>32</v>
       </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>27</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -980,6 +1514,19 @@
       <c r="C42" t="n">
         <v>69</v>
       </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>57</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -993,6 +1540,19 @@
       <c r="C43" t="n">
         <v>25</v>
       </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Aditya</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>34</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1006,6 +1566,19 @@
       <c r="C44" t="n">
         <v>11</v>
       </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Nisha</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>22</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1019,6 +1592,19 @@
       <c r="C45" t="n">
         <v>13</v>
       </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Vihaan</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>22</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1032,6 +1618,19 @@
       <c r="C46" t="n">
         <v>80</v>
       </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>44</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1045,6 +1644,19 @@
       <c r="C47" t="n">
         <v>21</v>
       </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Harper</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>20</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1058,6 +1670,19 @@
       <c r="C48" t="n">
         <v>14</v>
       </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Sahil</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>37</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1071,6 +1696,19 @@
       <c r="C49" t="n">
         <v>83</v>
       </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ria</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>38</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1084,6 +1722,19 @@
       <c r="C50" t="n">
         <v>46</v>
       </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Pooja</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>18</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1097,6 +1748,19 @@
       <c r="C51" t="n">
         <v>46</v>
       </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Pooja</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>18</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1110,6 +1774,19 @@
       <c r="C52" t="n">
         <v>59</v>
       </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>19</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1123,6 +1800,19 @@
       <c r="C53" t="n">
         <v>95</v>
       </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>37</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1136,6 +1826,19 @@
       <c r="C54" t="n">
         <v>22</v>
       </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Ishita</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>18</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1149,6 +1852,19 @@
       <c r="C55" t="n">
         <v>74</v>
       </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>40</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1162,6 +1878,19 @@
       <c r="C56" t="n">
         <v>30</v>
       </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Krish</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>43</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1175,6 +1904,19 @@
       <c r="C57" t="n">
         <v>15</v>
       </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>37</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1188,6 +1930,19 @@
       <c r="C58" t="n">
         <v>74</v>
       </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>40</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1201,6 +1956,19 @@
       <c r="C59" t="n">
         <v>77</v>
       </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>33</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1214,6 +1982,19 @@
       <c r="C60" t="n">
         <v>34</v>
       </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>31</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1227,6 +2008,19 @@
       <c r="C61" t="n">
         <v>62</v>
       </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Aryan</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>27</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1240,6 +2034,19 @@
       <c r="C62" t="n">
         <v>38</v>
       </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Meera</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>31</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1253,6 +2060,19 @@
       <c r="C63" t="n">
         <v>68</v>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>21</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1266,6 +2086,19 @@
       <c r="C64" t="n">
         <v>75</v>
       </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Raj</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>18</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1279,6 +2112,19 @@
       <c r="C65" t="n">
         <v>57</v>
       </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Tanya</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>26</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1292,6 +2138,19 @@
       <c r="C66" t="n">
         <v>65</v>
       </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>29</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1305,6 +2164,19 @@
       <c r="C67" t="n">
         <v>86</v>
       </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>47</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1318,6 +2190,19 @@
       <c r="C68" t="n">
         <v>34</v>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>31</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1331,6 +2216,19 @@
       <c r="C69" t="n">
         <v>54</v>
       </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>33</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1344,6 +2242,19 @@
       <c r="C70" t="n">
         <v>87</v>
       </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>39</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1357,6 +2268,19 @@
       <c r="C71" t="n">
         <v>17</v>
       </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>18</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1370,6 +2294,19 @@
       <c r="C72" t="n">
         <v>38</v>
       </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Meera</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>31</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1383,6 +2320,19 @@
       <c r="C73" t="n">
         <v>14</v>
       </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Sahil</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>37</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1396,6 +2346,19 @@
       <c r="C74" t="n">
         <v>32</v>
       </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>James</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>27</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1409,6 +2372,19 @@
       <c r="C75" t="n">
         <v>93</v>
       </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Henry</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>38</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1422,6 +2398,19 @@
       <c r="C76" t="n">
         <v>84</v>
       </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>30</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -1435,6 +2424,19 @@
       <c r="C77" t="n">
         <v>69</v>
       </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>57</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -1448,6 +2450,19 @@
       <c r="C78" t="n">
         <v>71</v>
       </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>42</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -1461,6 +2476,19 @@
       <c r="C79" t="n">
         <v>99</v>
       </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>26</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -1474,6 +2502,19 @@
       <c r="C80" t="n">
         <v>35</v>
       </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Sanya</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>42</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -1487,6 +2528,19 @@
       <c r="C81" t="n">
         <v>77</v>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Michael</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>33</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -1500,6 +2554,19 @@
       <c r="C82" t="n">
         <v>44</v>
       </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Jackson</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>47</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -1513,6 +2580,19 @@
       <c r="C83" t="n">
         <v>83</v>
       </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Ria</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>38</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -1526,6 +2606,19 @@
       <c r="C84" t="n">
         <v>34</v>
       </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>31</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -1539,6 +2632,19 @@
       <c r="C85" t="n">
         <v>33</v>
       </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>46</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -1552,6 +2658,19 @@
       <c r="C86" t="n">
         <v>71</v>
       </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>42</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -1565,6 +2684,19 @@
       <c r="C87" t="n">
         <v>50</v>
       </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>18</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -1578,6 +2710,19 @@
       <c r="C88" t="n">
         <v>29</v>
       </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>53</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -1591,6 +2736,19 @@
       <c r="C89" t="n">
         <v>48</v>
       </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>24</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -1604,6 +2762,19 @@
       <c r="C90" t="n">
         <v>86</v>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Ella</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>47</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -1617,6 +2788,19 @@
       <c r="C91" t="n">
         <v>80</v>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>44</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -1630,6 +2814,19 @@
       <c r="C92" t="n">
         <v>34</v>
       </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>31</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -1643,6 +2840,19 @@
       <c r="C93" t="n">
         <v>41</v>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>31</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -1656,6 +2866,19 @@
       <c r="C94" t="n">
         <v>11</v>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Nisha</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>22</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -1669,6 +2892,19 @@
       <c r="C95" t="n">
         <v>56</v>
       </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>53</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -1682,6 +2918,19 @@
       <c r="C96" t="n">
         <v>78</v>
       </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>38</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -1695,6 +2944,19 @@
       <c r="C97" t="n">
         <v>36</v>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Chloe</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>46</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -1708,6 +2970,19 @@
       <c r="C98" t="n">
         <v>71</v>
       </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>42</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -1721,6 +2996,19 @@
       <c r="C99" t="n">
         <v>58</v>
       </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>29</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -1734,6 +3022,19 @@
       <c r="C100" t="n">
         <v>40</v>
       </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Nikhil</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>29</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -1747,6 +3048,19 @@
       <c r="C101" t="n">
         <v>50</v>
       </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>18</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -1760,6 +3074,19 @@
       <c r="C102" t="n">
         <v>69</v>
       </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>57</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -1773,6 +3100,19 @@
       <c r="C103" t="n">
         <v>49</v>
       </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Radhika</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>32</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -1786,6 +3126,19 @@
       <c r="C104" t="n">
         <v>51</v>
       </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>21</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -1799,6 +3152,19 @@
       <c r="C105" t="n">
         <v>42</v>
       </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Zoey</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>20</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -1812,6 +3178,19 @@
       <c r="C106" t="n">
         <v>68</v>
       </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>21</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -1825,6 +3204,19 @@
       <c r="C107" t="n">
         <v>74</v>
       </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>40</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -1838,6 +3230,19 @@
       <c r="C108" t="n">
         <v>22</v>
       </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Ishita</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>18</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -1851,6 +3256,19 @@
       <c r="C109" t="n">
         <v>22</v>
       </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Ishita</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>18</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -1864,6 +3282,19 @@
       <c r="C110" t="n">
         <v>54</v>
       </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>33</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -1877,6 +3308,19 @@
       <c r="C111" t="n">
         <v>91</v>
       </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Karthik</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>44</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -1890,6 +3334,19 @@
       <c r="C112" t="n">
         <v>88</v>
       </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>51</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -1903,6 +3360,19 @@
       <c r="C113" t="n">
         <v>14</v>
       </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Sahil</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>37</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -1916,6 +3386,19 @@
       <c r="C114" t="n">
         <v>42</v>
       </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Zoey</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>20</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -1929,6 +3412,19 @@
       <c r="C115" t="n">
         <v>98</v>
       </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>28</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -1942,6 +3438,19 @@
       <c r="C116" t="n">
         <v>98</v>
       </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>28</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -1955,6 +3464,19 @@
       <c r="C117" t="n">
         <v>26</v>
       </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>34</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -1968,6 +3490,19 @@
       <c r="C118" t="n">
         <v>35</v>
       </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Sanya</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>42</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -1981,6 +3516,19 @@
       <c r="C119" t="n">
         <v>24</v>
       </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Aria</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>47</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -1994,6 +3542,19 @@
       <c r="C120" t="n">
         <v>78</v>
       </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>38</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -2007,6 +3568,19 @@
       <c r="C121" t="n">
         <v>55</v>
       </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Vikas</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>39</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -2020,6 +3594,19 @@
       <c r="C122" t="n">
         <v>38</v>
       </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Meera</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>31</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -2033,6 +3620,19 @@
       <c r="C123" t="n">
         <v>100</v>
       </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Leela</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>27</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -2046,6 +3646,19 @@
       <c r="C124" t="n">
         <v>67</v>
       </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>24</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -2059,6 +3672,19 @@
       <c r="C125" t="n">
         <v>90</v>
       </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>39</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -2072,6 +3698,19 @@
       <c r="C126" t="n">
         <v>40</v>
       </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Nikhil</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>29</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -2085,6 +3724,19 @@
       <c r="C127" t="n">
         <v>15</v>
       </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>37</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -2098,6 +3750,19 @@
       <c r="C128" t="n">
         <v>88</v>
       </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>51</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -2111,6 +3776,19 @@
       <c r="C129" t="n">
         <v>75</v>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Raj</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>18</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -2124,6 +3802,19 @@
       <c r="C130" t="n">
         <v>29</v>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>53</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -2137,6 +3828,19 @@
       <c r="C131" t="n">
         <v>85</v>
       </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>53</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -2150,6 +3854,19 @@
       <c r="C132" t="n">
         <v>42</v>
       </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Zoey</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>20</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -2163,6 +3880,19 @@
       <c r="C133" t="n">
         <v>100</v>
       </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Leela</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>27</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -2176,6 +3906,19 @@
       <c r="C134" t="n">
         <v>43</v>
       </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>35</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -2189,6 +3932,19 @@
       <c r="C135" t="n">
         <v>57</v>
       </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Tanya</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>26</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -2202,6 +3958,19 @@
       <c r="C136" t="n">
         <v>95</v>
       </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Evelyn</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>37</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -2215,6 +3984,19 @@
       <c r="C137" t="n">
         <v>54</v>
       </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>33</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -2228,6 +4010,19 @@
       <c r="C138" t="n">
         <v>47</v>
       </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Olivia</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>44</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -2241,6 +4036,19 @@
       <c r="C139" t="n">
         <v>81</v>
       </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>34</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -2254,6 +4062,19 @@
       <c r="C140" t="n">
         <v>26</v>
       </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>34</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -2267,6 +4088,19 @@
       <c r="C141" t="n">
         <v>15</v>
       </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>37</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -2280,6 +4114,19 @@
       <c r="C142" t="n">
         <v>82</v>
       </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Rhea</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>53</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -2293,6 +4140,19 @@
       <c r="C143" t="n">
         <v>74</v>
       </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>40</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -2306,6 +4166,19 @@
       <c r="C144" t="n">
         <v>78</v>
       </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Sebastian</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>38</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -2319,6 +4192,19 @@
       <c r="C145" t="n">
         <v>11</v>
       </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Nisha</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>22</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -2332,6 +4218,19 @@
       <c r="C146" t="n">
         <v>18</v>
       </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Carter</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>18</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -2345,6 +4244,19 @@
       <c r="C147" t="n">
         <v>21</v>
       </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Harper</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>20</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -2358,6 +4270,19 @@
       <c r="C148" t="n">
         <v>13</v>
       </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Vihaan</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>22</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -2371,6 +4296,19 @@
       <c r="C149" t="n">
         <v>41</v>
       </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>31</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -2384,6 +4322,19 @@
       <c r="C150" t="n">
         <v>28</v>
       </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>39</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -2397,6 +4348,19 @@
       <c r="C151" t="n">
         <v>49</v>
       </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Radhika</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>32</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -2410,6 +4374,19 @@
       <c r="C152" t="n">
         <v>24</v>
       </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Aria</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>47</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -2423,6 +4400,19 @@
       <c r="C153" t="n">
         <v>17</v>
       </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>18</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -2436,6 +4426,19 @@
       <c r="C154" t="n">
         <v>15</v>
       </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>37</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -2449,6 +4452,19 @@
       <c r="C155" t="n">
         <v>27</v>
       </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Kavya</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>41</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -2462,6 +4478,19 @@
       <c r="C156" t="n">
         <v>60</v>
       </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Mila</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>44</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -2475,6 +4504,19 @@
       <c r="C157" t="n">
         <v>96</v>
       </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Manish</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>36</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -2488,6 +4530,19 @@
       <c r="C158" t="n">
         <v>12</v>
       </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Kiran</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>52</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -2501,6 +4556,19 @@
       <c r="C159" t="n">
         <v>71</v>
       </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>42</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -2514,6 +4582,19 @@
       <c r="C160" t="n">
         <v>34</v>
       </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>31</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -2527,6 +4608,19 @@
       <c r="C161" t="n">
         <v>81</v>
       </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>34</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -2540,6 +4634,19 @@
       <c r="C162" t="n">
         <v>16</v>
       </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Ananya</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>32</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -2553,6 +4660,19 @@
       <c r="C163" t="n">
         <v>74</v>
       </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>40</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -2566,6 +4686,19 @@
       <c r="C164" t="n">
         <v>17</v>
       </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>18</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -2579,6 +4712,19 @@
       <c r="C165" t="n">
         <v>81</v>
       </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Jay</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>34</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -2592,6 +4738,19 @@
       <c r="C166" t="n">
         <v>85</v>
       </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>53</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -2605,6 +4764,19 @@
       <c r="C167" t="n">
         <v>50</v>
       </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>18</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -2618,6 +4790,19 @@
       <c r="C168" t="n">
         <v>17</v>
       </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>18</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -2631,6 +4816,19 @@
       <c r="C169" t="n">
         <v>27</v>
       </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Kavya</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>41</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -2644,6 +4842,19 @@
       <c r="C170" t="n">
         <v>41</v>
       </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>31</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -2657,6 +4868,19 @@
       <c r="C171" t="n">
         <v>39</v>
       </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Diya</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>31</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -2670,6 +4894,19 @@
       <c r="C172" t="n">
         <v>14</v>
       </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Sahil</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>37</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -2683,6 +4920,19 @@
       <c r="C173" t="n">
         <v>21</v>
       </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Harper</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>20</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -2696,6 +4946,19 @@
       <c r="C174" t="n">
         <v>27</v>
       </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Kavya</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>41</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -2709,6 +4972,19 @@
       <c r="C175" t="n">
         <v>92</v>
       </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>18</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -2722,6 +4998,19 @@
       <c r="C176" t="n">
         <v>48</v>
       </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>24</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -2735,6 +5024,19 @@
       <c r="C177" t="n">
         <v>31</v>
       </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Logan</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>36</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -2748,6 +5050,19 @@
       <c r="C178" t="n">
         <v>73</v>
       </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>29</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -2761,6 +5076,19 @@
       <c r="C179" t="n">
         <v>29</v>
       </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>53</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -2774,6 +5102,19 @@
       <c r="C180" t="n">
         <v>63</v>
       </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Layla</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>18</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -2787,6 +5128,19 @@
       <c r="C181" t="n">
         <v>73</v>
       </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Ethan</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>29</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -2800,6 +5154,19 @@
       <c r="C182" t="n">
         <v>25</v>
       </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Aditya</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>34</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -2813,6 +5180,19 @@
       <c r="C183" t="n">
         <v>98</v>
       </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>28</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -2826,6 +5206,19 @@
       <c r="C184" t="n">
         <v>61</v>
       </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>29</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -2839,6 +5232,19 @@
       <c r="C185" t="n">
         <v>55</v>
       </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Vikas</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>39</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -2852,6 +5258,19 @@
       <c r="C186" t="n">
         <v>61</v>
       </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>29</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -2865,6 +5284,19 @@
       <c r="C187" t="n">
         <v>71</v>
       </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>42</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -2878,6 +5310,19 @@
       <c r="C188" t="n">
         <v>41</v>
       </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>31</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -2891,6 +5336,19 @@
       <c r="C189" t="n">
         <v>98</v>
       </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>28</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -2904,6 +5362,19 @@
       <c r="C190" t="n">
         <v>28</v>
       </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>39</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -2917,6 +5388,19 @@
       <c r="C191" t="n">
         <v>43</v>
       </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>35</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -2930,6 +5414,19 @@
       <c r="C192" t="n">
         <v>57</v>
       </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Tanya</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>26</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -2943,6 +5440,19 @@
       <c r="C193" t="n">
         <v>48</v>
       </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>24</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -2956,6 +5466,19 @@
       <c r="C194" t="n">
         <v>92</v>
       </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>18</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -2969,6 +5492,19 @@
       <c r="C195" t="n">
         <v>90</v>
       </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>39</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -2982,6 +5518,19 @@
       <c r="C196" t="n">
         <v>26</v>
       </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>34</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -2995,6 +5544,19 @@
       <c r="C197" t="n">
         <v>26</v>
       </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>34</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -3008,6 +5570,19 @@
       <c r="C198" t="n">
         <v>41</v>
       </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>31</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -3021,6 +5596,19 @@
       <c r="C199" t="n">
         <v>21</v>
       </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Harper</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>20</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -3034,6 +5622,19 @@
       <c r="C200" t="n">
         <v>48</v>
       </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>24</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -3047,6 +5648,19 @@
       <c r="C201" t="n">
         <v>72</v>
       </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Amit</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>32</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -3060,6 +5674,19 @@
       <c r="C202" t="n">
         <v>71</v>
       </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>42</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -3073,6 +5700,19 @@
       <c r="C203" t="n">
         <v>68</v>
       </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>21</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -3086,6 +5726,19 @@
       <c r="C204" t="n">
         <v>52</v>
       </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>Aditi</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>36</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -3099,6 +5752,19 @@
       <c r="C205" t="n">
         <v>96</v>
       </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>Manish</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>36</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -3112,6 +5778,19 @@
       <c r="C206" t="n">
         <v>23</v>
       </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>Sonia</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>39</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -3125,6 +5804,19 @@
       <c r="C207" t="n">
         <v>71</v>
       </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>42</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -3138,6 +5830,19 @@
       <c r="C208" t="n">
         <v>33</v>
       </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>46</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -3151,6 +5856,19 @@
       <c r="C209" t="n">
         <v>66</v>
       </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>52</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -3164,6 +5882,19 @@
       <c r="C210" t="n">
         <v>62</v>
       </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Aryan</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>27</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -3177,6 +5908,19 @@
       <c r="C211" t="n">
         <v>55</v>
       </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Vikas</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>39</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -3190,6 +5934,19 @@
       <c r="C212" t="n">
         <v>51</v>
       </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Jack</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>21</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -3203,6 +5960,19 @@
       <c r="C213" t="n">
         <v>39</v>
       </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>Diya</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>31</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -3216,6 +5986,19 @@
       <c r="C214" t="n">
         <v>41</v>
       </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>31</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -3229,6 +6012,19 @@
       <c r="C215" t="n">
         <v>68</v>
       </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>21</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -3242,6 +6038,19 @@
       <c r="C216" t="n">
         <v>98</v>
       </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Ava</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>28</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -3255,6 +6064,19 @@
       <c r="C217" t="n">
         <v>88</v>
       </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>Aisha</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>51</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -3268,6 +6090,19 @@
       <c r="C218" t="n">
         <v>65</v>
       </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>Daniel</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>29</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -3281,6 +6116,19 @@
       <c r="C219" t="n">
         <v>71</v>
       </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>42</v>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -3294,6 +6142,19 @@
       <c r="C220" t="n">
         <v>28</v>
       </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>39</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -3307,6 +6168,19 @@
       <c r="C221" t="n">
         <v>69</v>
       </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>57</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -3320,6 +6194,19 @@
       <c r="C222" t="n">
         <v>68</v>
       </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Elijah</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>21</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -3333,6 +6220,19 @@
       <c r="C223" t="n">
         <v>61</v>
       </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>29</v>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -3346,6 +6246,19 @@
       <c r="C224" t="n">
         <v>25</v>
       </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Aditya</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>34</v>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -3359,6 +6272,19 @@
       <c r="C225" t="n">
         <v>66</v>
       </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Owen</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>52</v>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -3372,6 +6298,19 @@
       <c r="C226" t="n">
         <v>87</v>
       </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>39</v>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -3385,6 +6324,19 @@
       <c r="C227" t="n">
         <v>80</v>
       </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>44</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -3398,6 +6350,19 @@
       <c r="C228" t="n">
         <v>46</v>
       </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Pooja</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>18</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -3411,6 +6376,19 @@
       <c r="C229" t="n">
         <v>48</v>
       </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Ravi</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>24</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -3424,6 +6402,19 @@
       <c r="C230" t="n">
         <v>20</v>
       </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Hannah</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>28</v>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -3437,6 +6428,19 @@
       <c r="C231" t="n">
         <v>83</v>
       </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Ria</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>38</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -3450,6 +6454,19 @@
       <c r="C232" t="n">
         <v>91</v>
       </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Karthik</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>44</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -3463,6 +6480,19 @@
       <c r="C233" t="n">
         <v>54</v>
       </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Priya</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>33</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -3476,6 +6506,19 @@
       <c r="C234" t="n">
         <v>34</v>
       </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>31</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -3489,6 +6532,19 @@
       <c r="C235" t="n">
         <v>63</v>
       </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Layla</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>18</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -3502,6 +6558,19 @@
       <c r="C236" t="n">
         <v>26</v>
       </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Matthew</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>34</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -3515,6 +6584,19 @@
       <c r="C237" t="n">
         <v>18</v>
       </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Carter</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>18</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -3528,6 +6610,19 @@
       <c r="C238" t="n">
         <v>30</v>
       </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Krish</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>43</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -3541,6 +6636,19 @@
       <c r="C239" t="n">
         <v>89</v>
       </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Aarav</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>37</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -3554,6 +6662,19 @@
       <c r="C240" t="n">
         <v>11</v>
       </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Nisha</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>22</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -3567,6 +6688,19 @@
       <c r="C241" t="n">
         <v>49</v>
       </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Radhika</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>32</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -3580,6 +6714,19 @@
       <c r="C242" t="n">
         <v>96</v>
       </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Manish</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>36</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -3593,6 +6740,19 @@
       <c r="C243" t="n">
         <v>100</v>
       </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Leela</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>27</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -3606,6 +6766,19 @@
       <c r="C244" t="n">
         <v>50</v>
       </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>18</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -3619,6 +6792,19 @@
       <c r="C245" t="n">
         <v>71</v>
       </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>42</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -3632,6 +6818,19 @@
       <c r="C246" t="n">
         <v>59</v>
       </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>William</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>19</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -3645,6 +6844,19 @@
       <c r="C247" t="n">
         <v>58</v>
       </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Sophia</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>29</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -3658,6 +6870,19 @@
       <c r="C248" t="n">
         <v>17</v>
       </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>18</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -3671,6 +6896,19 @@
       <c r="C249" t="n">
         <v>62</v>
       </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Aryan</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>27</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -3684,6 +6922,19 @@
       <c r="C250" t="n">
         <v>71</v>
       </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>42</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -3697,6 +6948,19 @@
       <c r="C251" t="n">
         <v>92</v>
       </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Isabella</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>18</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -3710,6 +6974,19 @@
       <c r="C252" t="n">
         <v>30</v>
       </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Krish</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>43</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -3723,6 +7000,19 @@
       <c r="C253" t="n">
         <v>34</v>
       </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>31</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -3736,6 +7026,19 @@
       <c r="C254" t="n">
         <v>36</v>
       </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Chloe</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>46</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -3749,6 +7052,19 @@
       <c r="C255" t="n">
         <v>56</v>
       </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>53</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -3762,6 +7078,19 @@
       <c r="C256" t="n">
         <v>87</v>
       </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Kabir</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>39</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -3775,6 +7104,19 @@
       <c r="C257" t="n">
         <v>40</v>
       </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Nikhil</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>29</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -3788,6 +7130,19 @@
       <c r="C258" t="n">
         <v>100</v>
       </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Leela</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>27</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -3801,6 +7156,19 @@
       <c r="C259" t="n">
         <v>43</v>
       </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>35</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -3814,6 +7182,19 @@
       <c r="C260" t="n">
         <v>75</v>
       </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>Raj</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>18</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -3827,6 +7208,19 @@
       <c r="C261" t="n">
         <v>94</v>
       </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>Surya</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>25</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -3840,6 +7234,19 @@
       <c r="C262" t="n">
         <v>61</v>
       </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Rohan</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>29</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -3853,6 +7260,19 @@
       <c r="C263" t="n">
         <v>15</v>
       </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>37</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -3866,6 +7286,19 @@
       <c r="C264" t="n">
         <v>15</v>
       </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>37</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -3879,6 +7312,19 @@
       <c r="C265" t="n">
         <v>41</v>
       </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>31</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -3892,6 +7338,19 @@
       <c r="C266" t="n">
         <v>89</v>
       </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Aarav</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>37</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -3905,6 +7364,19 @@
       <c r="C267" t="n">
         <v>99</v>
       </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Dev</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>26</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -3918,6 +7390,19 @@
       <c r="C268" t="n">
         <v>69</v>
       </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>57</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -3931,6 +7416,19 @@
       <c r="C269" t="n">
         <v>43</v>
       </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Alexander</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>35</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -3944,6 +7442,19 @@
       <c r="C270" t="n">
         <v>89</v>
       </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Aarav</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>37</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -3957,6 +7468,19 @@
       <c r="C271" t="n">
         <v>82</v>
       </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Rhea</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>53</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -3970,6 +7494,19 @@
       <c r="C272" t="n">
         <v>41</v>
       </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Maya</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>31</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -3983,6 +7520,19 @@
       <c r="C273" t="n">
         <v>46</v>
       </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Pooja</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>18</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -3996,6 +7546,19 @@
       <c r="C274" t="n">
         <v>90</v>
       </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>39</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -4009,6 +7572,19 @@
       <c r="C275" t="n">
         <v>28</v>
       </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Charlotte</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>39</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -4022,6 +7598,19 @@
       <c r="C276" t="n">
         <v>90</v>
       </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Samuel</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>39</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -4035,6 +7624,19 @@
       <c r="C277" t="n">
         <v>30</v>
       </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Krish</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>43</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -4048,6 +7650,19 @@
       <c r="C278" t="n">
         <v>34</v>
       </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Abigail</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>31</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -4061,6 +7676,19 @@
       <c r="C279" t="n">
         <v>74</v>
       </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Arjun</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>40</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -4074,6 +7702,19 @@
       <c r="C280" t="n">
         <v>82</v>
       </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Rhea</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>53</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -4087,6 +7728,19 @@
       <c r="C281" t="n">
         <v>70</v>
       </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Anjali</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>28</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -4100,6 +7754,19 @@
       <c r="C282" t="n">
         <v>39</v>
       </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Diya</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>31</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -4113,6 +7780,19 @@
       <c r="C283" t="n">
         <v>37</v>
       </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Luke</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>45</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -4126,6 +7806,19 @@
       <c r="C284" t="n">
         <v>33</v>
       </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Lily</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>46</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -4139,6 +7832,19 @@
       <c r="C285" t="n">
         <v>29</v>
       </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Noah</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>53</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -4152,6 +7858,19 @@
       <c r="C286" t="n">
         <v>56</v>
       </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Emma</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>53</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -4165,6 +7884,19 @@
       <c r="C287" t="n">
         <v>55</v>
       </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Vikas</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>39</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -4178,6 +7910,19 @@
       <c r="C288" t="n">
         <v>69</v>
       </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>57</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -4191,6 +7936,19 @@
       <c r="C289" t="n">
         <v>69</v>
       </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Amelia</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>57</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -4204,6 +7962,19 @@
       <c r="C290" t="n">
         <v>84</v>
       </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Grace</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>30</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -4217,6 +7988,19 @@
       <c r="C291" t="n">
         <v>67</v>
       </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Mason</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>24</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -4230,6 +8014,19 @@
       <c r="C292" t="n">
         <v>96</v>
       </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Manish</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>36</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -4243,6 +8040,19 @@
       <c r="C293" t="n">
         <v>15</v>
       </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Anika</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>37</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -4256,6 +8066,19 @@
       <c r="C294" t="n">
         <v>82</v>
       </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Rhea</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>53</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -4269,6 +8092,19 @@
       <c r="C295" t="n">
         <v>55</v>
       </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Vikas</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>39</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -4282,6 +8118,19 @@
       <c r="C296" t="n">
         <v>11</v>
       </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Nisha</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>22</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -4295,6 +8144,19 @@
       <c r="C297" t="n">
         <v>17</v>
       </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Sneha</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>18</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -4307,6 +8169,19 @@
       </c>
       <c r="C298" t="n">
         <v>71</v>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Liam</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>42</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4320,1595 +8195,674 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>customer_id</t>
+          <t>product_id</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>product_name</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>customer_age</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>customer_gender</t>
+          <t>price_rs</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Apples</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Bananas</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>33</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>71</v>
+        <v>248</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Liam</t>
+          <t>Oranges</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>42</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56</v>
+        <v>242</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Emma</t>
+          <t>Grapes</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>53</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>79</v>
+        <v>299</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ayaan</t>
+          <t>Strawberries</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>300</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ananya</t>
+          <t>Blueberries</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>29</v>
+        <v>207</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Noah</t>
+          <t>Pineapples</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>53</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>47</v>
+        <v>199</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Olivia</t>
+          <t>Mangoes</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>150</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61</v>
+        <v>215</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rohan</t>
+          <t>Watermelons</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>27</v>
+        <v>128</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Lemons</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>41</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73</v>
+        <v>116</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>Potatoes</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>29</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>58</v>
+        <v>167</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sophia</t>
+          <t>Tomatoes</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>29</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>89</v>
+        <v>222</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Aarav</t>
+          <t>Onions</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>40</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Ishita</t>
+          <t>Carrots</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>18</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>50</v>
+        <v>245</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lucas</t>
+          <t>Lettuce</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>18</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>98</v>
+        <v>142</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Ava</t>
+          <t>Broccoli</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>150</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13</v>
+        <v>274</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vihaan</t>
+          <t>Spinach</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>22</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>160</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ria</t>
+          <t>Cabbage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>38</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>67</v>
+        <v>276</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Mason</t>
+          <t>Cucumbers</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>40</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Mia</t>
+          <t>Peppers</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>18</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>200</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kiran</t>
+          <t>Bread</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>52</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>10</v>
+        <v>137</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Simran</t>
+          <t>Milk</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>32</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>60</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>43</v>
+        <v>264</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Eggs</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>35</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>92</v>
+        <v>232</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Isabella</t>
+          <t>Butter</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>18</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>400</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>64</v>
+        <v>183</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Dhruv</t>
+          <t>Cheese</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>28</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>800</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Aditi</t>
+          <t>Rice</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>36</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>68</v>
+        <v>259</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Elijah</t>
+          <t>Pasta</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>21</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>120</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Charlotte</t>
+          <t>Flour</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>39</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>40</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>62</v>
+        <v>288</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Aryan</t>
+          <t>Sugar</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>27</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>50</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Meera</t>
+          <t>Salt</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>31</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>32</v>
+        <v>253</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>James</t>
+          <t>Olive oil</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>27</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>600</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>69</v>
+        <v>220</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amelia</t>
+          <t>Coffee</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>57</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>800</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>25</v>
+        <v>296</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Aditya</t>
+          <t>Tea</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>34</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>400</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>11</v>
+        <v>227</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nisha</t>
+          <t>Cereal</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>22</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>300</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>80</v>
+        <v>252</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Benjamin</t>
+          <t>Peanut butter</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>44</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>300</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>21</v>
+        <v>173</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Jelly</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>200</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>14</v>
+        <v>165</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sahil</t>
+          <t>Chicken</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>37</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>250</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pooja</t>
+          <t>Beef</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>18</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>500</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>59</v>
+        <v>261</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>William</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>19</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>700</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>95</v>
+        <v>231</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Evelyn</t>
+          <t>Pork</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>37</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>350</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>30</v>
+        <v>287</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Krish</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>43</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>400</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>15</v>
+        <v>176</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Toothpaste</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>37</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>800</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>77</v>
+        <v>126</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Michael</t>
+          <t>Soap</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>33</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>400</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>34</v>
+        <v>161</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Abigail</t>
+          <t>Laundry detergent</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>31</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>400</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>75</v>
+        <v>255</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Raj</t>
+          <t>Paper towels</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>18</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>300</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>57</v>
+        <v>140</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tanya</t>
+          <t>Toilet paper</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>26</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>200</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Light bulbs</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>29</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>800</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>86</v>
+        <v>179</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ella</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>47</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
+        <v>1000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>87</v>
+        <v>201</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Kabir</t>
+          <t>Dish soap</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>39</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>200</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>17</v>
+        <v>143</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Aluminum foil</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>18</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>93</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Henry</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>38</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>84</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Grace</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>30</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>99</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Dev</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>26</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>35</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Sanya</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>42</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>44</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Jackson</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>47</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>33</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Lily</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>46</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>48</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Ravi</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>24</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>41</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Maya</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>31</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>78</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Sebastian</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>38</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>36</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Chloe</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>46</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>40</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Nikhil</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>29</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>49</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Radhika</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>32</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>51</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Jack</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>21</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>42</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Zoey</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>20</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>91</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Karthik</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>44</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>88</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Aisha</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>51</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>26</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Matthew</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>34</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>24</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Aria</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>47</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>55</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Vikas</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>39</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>100</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Leela</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>27</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>90</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Samuel</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
-        <v>39</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>85</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>53</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>81</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Jay</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>34</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>82</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Rhea</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>53</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>18</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Carter</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>18</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>60</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Mila</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
-        <v>44</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>96</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Manish</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>36</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>39</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Diya</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>31</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>31</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Logan</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>36</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>63</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Layla</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
-        <v>18</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="n">
-        <v>72</v>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Amit</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>32</v>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n">
-        <v>23</v>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Sonia</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>39</v>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n">
-        <v>66</v>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Owen</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>52</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="n">
-        <v>20</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Hannah</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>28</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>94</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Surya</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>25</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>70</v>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Anjali</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>28</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Female</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>37</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Luke</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>45</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
+        <v>600</v>
       </c>
     </row>
   </sheetData>
@@ -5922,687 +8876,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>product_id</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>product_name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>price_rs</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>148</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Apples</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>149</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Bananas</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>248</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Oranges</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>242</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Grapes</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>299</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Strawberries</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>158</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Blueberries</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>207</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Pineapples</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>199</v>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Mangoes</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>215</v>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Watermelons</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>128</v>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Lemons</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>116</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Potatoes</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>167</v>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Tomatoes</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>222</v>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Onions</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>187</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Carrots</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>245</v>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Lettuce</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>142</v>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Broccoli</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>274</v>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Spinach</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>284</v>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Cabbage</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>276</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Cucumbers</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>136</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Peppers</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>188</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bread</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>137</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Milk</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>264</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Eggs</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>232</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Butter</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>183</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Cheese</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>195</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Rice</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>259</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Pasta</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>196</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Flour</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>288</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Sugar</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>147</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Salt</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>253</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Olive oil</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>220</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Coffee</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>296</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Tea</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>227</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Cereal</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>252</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Peanut butter</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>173</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Jelly</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>165</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Chicken</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>117</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Beef</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>261</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Fish</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>231</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Pork</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>287</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Shampoo</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>176</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Toothpaste</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>126</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Soap</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>161</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Laundry detergent</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>255</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Paper towels</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>140</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Toilet paper</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>260</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Light bulbs</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>179</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Batteries</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>201</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Dish soap</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>143</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Aluminum foil</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>600</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:D301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
